--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121224936</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,53 +968,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R4" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1057,12 +1048,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,7 +1095,7 @@
         <v>121222886</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>90705</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,44 +1248,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R6" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,33 +1337,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292409</v>
+        <v>121292347</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473882</v>
+        <v>473895</v>
       </c>
       <c r="R7" t="n">
-        <v>7042892</v>
+        <v>7042857</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292483</v>
+        <v>121292220</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>98083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1516,35 +1516,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1552,14 +1560,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473855</v>
+        <v>473457</v>
       </c>
       <c r="R8" t="n">
-        <v>7042902</v>
+        <v>7043473</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1605,6 +1613,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1613,24 +1622,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1648,10 +1642,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121225143</v>
+        <v>121292483</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1696,17 +1690,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R9" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1792,10 +1786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292522</v>
+        <v>121292409</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1808,37 +1802,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473855</v>
+        <v>473882</v>
       </c>
       <c r="R10" t="n">
-        <v>7042902</v>
+        <v>7042892</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1875,7 +1878,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1884,7 +1887,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1905,12 +1907,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1931,7 +1933,7 @@
         <v>121292659</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2064,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292220</v>
+        <v>121292522</v>
       </c>
       <c r="B12" t="n">
-        <v>98073</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2076,58 +2078,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473457</v>
+        <v>473855</v>
       </c>
       <c r="R12" t="n">
-        <v>7043473</v>
+        <v>7042902</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2164,7 +2149,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2182,9 +2167,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292347</v>
+        <v>121225143</v>
       </c>
       <c r="B13" t="n">
-        <v>57364</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2218,16 +2218,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473895</v>
+        <v>473844</v>
       </c>
       <c r="R13" t="n">
-        <v>7042857</v>
+        <v>7042901</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121225455</v>
+        <v>121226161</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,46 +2362,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473813</v>
+        <v>473786</v>
       </c>
       <c r="R14" t="n">
-        <v>7042912</v>
+        <v>7042884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2436,11 +2424,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2467,12 +2450,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2493,7 +2476,7 @@
         <v>121298031</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2634,10 +2617,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121226161</v>
+        <v>121298076</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2650,37 +2633,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473786</v>
+        <v>473772</v>
       </c>
       <c r="R16" t="n">
-        <v>7042884</v>
+        <v>7042897</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2712,12 +2702,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2738,12 +2734,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2761,10 +2757,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298075</v>
+        <v>121225335</v>
       </c>
       <c r="B17" t="n">
-        <v>56552</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2777,16 +2773,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2794,16 +2790,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2813,17 +2805,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473885</v>
+        <v>473813</v>
       </c>
       <c r="R17" t="n">
-        <v>7042869</v>
+        <v>7042912</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2872,6 +2864,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2889,10 +2901,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298076</v>
+        <v>121298075</v>
       </c>
       <c r="B18" t="n">
-        <v>90705</v>
+        <v>56555</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2905,44 +2917,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473772</v>
+        <v>473885</v>
       </c>
       <c r="R18" t="n">
-        <v>7042897</v>
+        <v>7042869</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2985,33 +3006,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260654</v>
+        <v>121222886</v>
       </c>
       <c r="B4" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,44 +968,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473423</v>
+        <v>473389</v>
       </c>
       <c r="R4" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1048,7 +1049,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222886</v>
+        <v>121222957</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,39 +1108,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473389</v>
+        <v>473391</v>
       </c>
       <c r="R5" t="n">
         <v>7043433</v>
@@ -1195,26 +1203,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,10 +1220,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1236,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R6" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,12 +1316,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292220</v>
+        <v>121225143</v>
       </c>
       <c r="B8" t="n">
-        <v>98083</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1516,43 +1516,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1560,17 +1552,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473457</v>
+        <v>473844</v>
       </c>
       <c r="R8" t="n">
-        <v>7043473</v>
+        <v>7042901</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1613,7 +1605,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1622,9 +1613,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1642,7 +1648,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121292483</v>
+        <v>121292409</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1694,10 +1700,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473855</v>
+        <v>473882</v>
       </c>
       <c r="R9" t="n">
-        <v>7042902</v>
+        <v>7042892</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,10 +1792,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292409</v>
+        <v>121292659</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1802,46 +1808,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473882</v>
+        <v>473835</v>
       </c>
       <c r="R10" t="n">
-        <v>7042892</v>
+        <v>7042906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1878,7 +1875,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1887,6 +1884,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1907,12 +1905,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1930,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292659</v>
+        <v>121292220</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>98083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1942,41 +1940,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473835</v>
+        <v>473457</v>
       </c>
       <c r="R11" t="n">
-        <v>7042906</v>
+        <v>7043473</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2013,7 +2028,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,24 +2046,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292522</v>
+        <v>121292483</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,27 +2082,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -2149,7 +2158,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2158,7 +2167,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,12 +2187,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2202,10 +2210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121225143</v>
+        <v>121292522</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2218,49 +2226,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R13" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2294,7 +2293,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,6 +2302,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121226161</v>
+        <v>121298076</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,37 +2362,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473786</v>
+        <v>473772</v>
       </c>
       <c r="R14" t="n">
-        <v>7042884</v>
+        <v>7042897</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2424,12 +2431,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2450,12 +2463,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2473,7 +2486,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298031</v>
+        <v>121225455</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2511,7 +2524,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2521,17 +2534,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473837</v>
+        <v>473813</v>
       </c>
       <c r="R15" t="n">
-        <v>7042921</v>
+        <v>7042912</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2565,7 +2578,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2617,10 +2630,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298076</v>
+        <v>121298075</v>
       </c>
       <c r="B16" t="n">
-        <v>90715</v>
+        <v>56555</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2633,44 +2646,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473772</v>
+        <v>473885</v>
       </c>
       <c r="R16" t="n">
-        <v>7042897</v>
+        <v>7042869</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2713,33 +2735,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2757,7 +2758,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121225335</v>
+        <v>121298031</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2805,17 +2806,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473813</v>
+        <v>473837</v>
       </c>
       <c r="R17" t="n">
-        <v>7042912</v>
+        <v>7042921</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2849,7 +2850,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2901,10 +2902,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298075</v>
+        <v>121226161</v>
       </c>
       <c r="B18" t="n">
-        <v>56555</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,53 +2918,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473885</v>
+        <v>473786</v>
       </c>
       <c r="R18" t="n">
-        <v>7042869</v>
+        <v>7042884</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2995,11 +2980,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -3012,6 +2992,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,53 +1108,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R5" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1197,12 +1188,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,44 +1248,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R6" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,33 +1337,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292347</v>
+        <v>121292483</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473895</v>
+        <v>473855</v>
       </c>
       <c r="R7" t="n">
-        <v>7042857</v>
+        <v>7042902</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225143</v>
+        <v>121292347</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473844</v>
+        <v>473895</v>
       </c>
       <c r="R8" t="n">
-        <v>7042901</v>
+        <v>7042857</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121292409</v>
+        <v>121292220</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>98096</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1660,35 +1660,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1696,14 +1704,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473882</v>
+        <v>473457</v>
       </c>
       <c r="R9" t="n">
-        <v>7042892</v>
+        <v>7043473</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1749,6 +1757,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1757,24 +1766,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1795,7 +1789,7 @@
         <v>121292659</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1928,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292220</v>
+        <v>121292409</v>
       </c>
       <c r="B11" t="n">
-        <v>98083</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1940,43 +1934,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1984,14 +1970,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473457</v>
+        <v>473882</v>
       </c>
       <c r="R11" t="n">
-        <v>7043473</v>
+        <v>7042892</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2037,7 +2023,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2046,9 +2031,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292483</v>
+        <v>121292522</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,36 +2082,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -2158,7 +2149,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2167,6 +2158,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2187,12 +2179,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2210,10 +2202,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292522</v>
+        <v>121225143</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2226,40 +2218,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473855</v>
+        <v>473844</v>
       </c>
       <c r="R13" t="n">
-        <v>7042902</v>
+        <v>7042901</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2302,7 +2303,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
         <v>121298076</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121225455</v>
+        <v>121298075</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>56555</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2502,16 +2502,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2519,12 +2519,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2534,17 +2538,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473813</v>
+        <v>473885</v>
       </c>
       <c r="R15" t="n">
-        <v>7042912</v>
+        <v>7042869</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2593,26 +2597,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2630,10 +2614,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298075</v>
+        <v>121225335</v>
       </c>
       <c r="B16" t="n">
-        <v>56555</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2646,16 +2630,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2663,16 +2647,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2682,17 +2662,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473885</v>
+        <v>473813</v>
       </c>
       <c r="R16" t="n">
-        <v>7042869</v>
+        <v>7042912</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2741,6 +2721,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
         <v>121226161</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B5" t="n">
-        <v>90727</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,44 +1108,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R5" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1188,33 +1197,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,10 +1220,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1236,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R6" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,12 +1316,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292483</v>
+        <v>121292220</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>98097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,35 +1372,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1408,14 +1416,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473855</v>
+        <v>473457</v>
       </c>
       <c r="R7" t="n">
-        <v>7042902</v>
+        <v>7043473</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,6 +1469,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1469,24 +1478,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1504,10 +1498,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292347</v>
+        <v>121225143</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,16 +1514,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1552,17 +1546,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473895</v>
+        <v>473844</v>
       </c>
       <c r="R8" t="n">
-        <v>7042857</v>
+        <v>7042901</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1590,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1648,10 +1642,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121292220</v>
+        <v>121292409</v>
       </c>
       <c r="B9" t="n">
-        <v>98096</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1660,43 +1654,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1704,14 +1690,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473457</v>
+        <v>473882</v>
       </c>
       <c r="R9" t="n">
-        <v>7043473</v>
+        <v>7042892</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1757,7 +1743,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1766,9 +1751,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292409</v>
+        <v>121292483</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473882</v>
+        <v>473855</v>
       </c>
       <c r="R11" t="n">
-        <v>7042892</v>
+        <v>7042902</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292522</v>
+        <v>121292347</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,37 +2082,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473855</v>
+        <v>473895</v>
       </c>
       <c r="R12" t="n">
-        <v>7042902</v>
+        <v>7042857</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2149,7 +2158,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2158,7 +2167,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,12 +2187,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2202,10 +2210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121225143</v>
+        <v>121292522</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2218,49 +2226,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R13" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2294,7 +2293,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,6 +2302,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121298076</v>
+        <v>121225455</v>
       </c>
       <c r="B14" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,44 +2362,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473772</v>
+        <v>473813</v>
       </c>
       <c r="R14" t="n">
-        <v>7042897</v>
+        <v>7042912</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2442,7 +2447,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2463,12 +2467,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2486,10 +2490,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298075</v>
+        <v>121298031</v>
       </c>
       <c r="B15" t="n">
-        <v>56555</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2502,16 +2506,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2519,16 +2523,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473885</v>
+        <v>473837</v>
       </c>
       <c r="R15" t="n">
-        <v>7042869</v>
+        <v>7042921</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2597,6 +2597,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2614,10 +2634,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121225335</v>
+        <v>121226161</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2630,46 +2650,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473813</v>
+        <v>473786</v>
       </c>
       <c r="R16" t="n">
-        <v>7042912</v>
+        <v>7042884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2704,11 +2712,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2735,12 +2738,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2758,10 +2761,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298031</v>
+        <v>121298076</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2774,46 +2777,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473837</v>
+        <v>473772</v>
       </c>
       <c r="R17" t="n">
-        <v>7042921</v>
+        <v>7042897</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2850,7 +2848,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2859,6 +2857,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2879,12 +2878,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2902,10 +2901,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121226161</v>
+        <v>121298075</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>56555</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2918,37 +2917,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473786</v>
+        <v>473885</v>
       </c>
       <c r="R18" t="n">
-        <v>7042884</v>
+        <v>7042869</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2980,6 +2995,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2992,26 +3012,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121224936</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222886</v>
+        <v>121260654</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,45 +968,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473389</v>
+        <v>473423</v>
       </c>
       <c r="R4" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,6 +1048,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222957</v>
+        <v>121222886</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,47 +1108,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473391</v>
+        <v>473389</v>
       </c>
       <c r="R5" t="n">
         <v>7043433</v>
@@ -1203,6 +1195,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,44 +1248,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R6" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,33 +1337,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292220</v>
+        <v>121292659</v>
       </c>
       <c r="B7" t="n">
-        <v>98097</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,58 +1372,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473457</v>
+        <v>473835</v>
       </c>
       <c r="R7" t="n">
-        <v>7043473</v>
+        <v>7042906</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1460,7 +1443,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,9 +1461,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1498,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225143</v>
+        <v>121292409</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1536,7 +1534,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1546,17 +1544,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473844</v>
+        <v>473882</v>
       </c>
       <c r="R8" t="n">
-        <v>7042901</v>
+        <v>7042892</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1642,10 +1640,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121292409</v>
+        <v>121292347</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1658,16 +1656,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1680,7 +1678,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1694,10 +1692,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473882</v>
+        <v>473895</v>
       </c>
       <c r="R9" t="n">
-        <v>7042892</v>
+        <v>7042857</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1734,7 +1732,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,10 +1784,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292659</v>
+        <v>121292483</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1802,37 +1800,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473835</v>
+        <v>473855</v>
       </c>
       <c r="R10" t="n">
-        <v>7042906</v>
+        <v>7042902</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1869,7 +1876,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1878,7 +1885,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1899,12 +1905,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1922,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292483</v>
+        <v>121225143</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1960,7 +1966,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1970,17 +1976,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473855</v>
+        <v>473844</v>
       </c>
       <c r="R11" t="n">
-        <v>7042902</v>
+        <v>7042901</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2066,10 +2072,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292347</v>
+        <v>121292522</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,46 +2088,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473895</v>
+        <v>473855</v>
       </c>
       <c r="R12" t="n">
-        <v>7042857</v>
+        <v>7042902</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2158,7 +2155,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2167,6 +2164,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2187,12 +2185,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2210,10 +2208,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292522</v>
+        <v>121292220</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>98100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2222,41 +2220,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473855</v>
+        <v>473457</v>
       </c>
       <c r="R13" t="n">
-        <v>7042902</v>
+        <v>7043473</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2293,7 +2308,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2311,24 +2326,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121225455</v>
+        <v>121226161</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,46 +2362,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473813</v>
+        <v>473786</v>
       </c>
       <c r="R14" t="n">
-        <v>7042912</v>
+        <v>7042884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2436,11 +2424,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2467,12 +2450,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2490,10 +2473,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298031</v>
+        <v>121225455</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2528,7 +2511,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2538,17 +2521,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473837</v>
+        <v>473813</v>
       </c>
       <c r="R15" t="n">
-        <v>7042921</v>
+        <v>7042912</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2582,7 +2565,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2634,10 +2617,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121226161</v>
+        <v>121298075</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>56558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2650,37 +2633,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473786</v>
+        <v>473885</v>
       </c>
       <c r="R16" t="n">
-        <v>7042884</v>
+        <v>7042869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2712,6 +2711,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2724,26 +2728,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2764,7 +2748,7 @@
         <v>121298076</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2901,10 +2885,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298075</v>
+        <v>121298031</v>
       </c>
       <c r="B18" t="n">
-        <v>56555</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,16 +2901,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2934,16 +2918,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2957,13 +2937,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473885</v>
+        <v>473837</v>
       </c>
       <c r="R18" t="n">
-        <v>7042869</v>
+        <v>7042921</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2997,7 +2977,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3012,6 +2992,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,44 +968,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R4" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1048,33 +1057,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1232,10 +1220,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1236,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R6" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,12 +1316,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292659</v>
+        <v>121292409</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,37 +1376,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473835</v>
+        <v>473882</v>
       </c>
       <c r="R7" t="n">
-        <v>7042906</v>
+        <v>7042892</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1443,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1461,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1473,12 +1481,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,7 +1504,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292409</v>
+        <v>121225143</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1534,7 +1542,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1544,17 +1552,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473882</v>
+        <v>473844</v>
       </c>
       <c r="R8" t="n">
-        <v>7042892</v>
+        <v>7042901</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1784,10 +1792,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292483</v>
+        <v>121292522</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1800,36 +1808,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -1876,7 +1875,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,6 +1884,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121225143</v>
+        <v>121292659</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1944,49 +1944,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473844</v>
+        <v>473835</v>
       </c>
       <c r="R11" t="n">
-        <v>7042901</v>
+        <v>7042906</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2020,7 +2011,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2029,6 +2020,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2049,12 +2041,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2072,10 +2064,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292522</v>
+        <v>121292483</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2088,27 +2080,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -2155,7 +2156,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2164,7 +2165,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121225455</v>
+        <v>121298075</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>56558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2489,16 +2489,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2506,12 +2506,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2521,17 +2525,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473813</v>
+        <v>473885</v>
       </c>
       <c r="R15" t="n">
-        <v>7042912</v>
+        <v>7042869</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2580,26 +2584,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2617,10 +2601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298075</v>
+        <v>121298076</v>
       </c>
       <c r="B16" t="n">
-        <v>56558</v>
+        <v>90731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2633,53 +2617,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473885</v>
+        <v>473772</v>
       </c>
       <c r="R16" t="n">
-        <v>7042869</v>
+        <v>7042897</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2722,12 +2697,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2745,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298076</v>
+        <v>121225455</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2761,44 +2757,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473772</v>
+        <v>473813</v>
       </c>
       <c r="R17" t="n">
-        <v>7042897</v>
+        <v>7042912</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2841,7 +2842,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298076</v>
+        <v>121225455</v>
       </c>
       <c r="B16" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2617,44 +2617,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473772</v>
+        <v>473813</v>
       </c>
       <c r="R16" t="n">
-        <v>7042897</v>
+        <v>7042912</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2697,7 +2702,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2718,12 +2722,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,10 +2745,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121225455</v>
+        <v>121298076</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2757,49 +2761,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473813</v>
+        <v>473772</v>
       </c>
       <c r="R17" t="n">
-        <v>7042912</v>
+        <v>7042897</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2842,6 +2841,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121225455</v>
+        <v>121298076</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2617,49 +2617,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473813</v>
+        <v>473772</v>
       </c>
       <c r="R16" t="n">
-        <v>7042912</v>
+        <v>7042897</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2702,6 +2697,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2722,12 +2718,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2745,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298076</v>
+        <v>121225455</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2761,44 +2757,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473772</v>
+        <v>473813</v>
       </c>
       <c r="R17" t="n">
-        <v>7042897</v>
+        <v>7042912</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2841,7 +2842,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121224936</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>90737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,53 +968,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R4" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1057,12 +1048,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,7 +1095,7 @@
         <v>121222886</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>57508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,44 +1248,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R6" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,33 +1337,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
         <v>121292409</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121225143</v>
+        <v>121292659</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,49 +1520,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473844</v>
+        <v>473835</v>
       </c>
       <c r="R8" t="n">
-        <v>7042901</v>
+        <v>7042906</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1587,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,6 +1596,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1625,12 +1617,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1651,7 +1643,7 @@
         <v>121292347</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1792,10 +1784,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292522</v>
+        <v>121292483</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1808,27 +1800,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -1875,7 +1876,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1884,7 +1885,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292659</v>
+        <v>121292522</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1967,14 +1967,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473835</v>
+        <v>473855</v>
       </c>
       <c r="R11" t="n">
-        <v>7042906</v>
+        <v>7042902</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292483</v>
+        <v>121225143</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473855</v>
+        <v>473844</v>
       </c>
       <c r="R12" t="n">
-        <v>7042902</v>
+        <v>7042901</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>121292220</v>
       </c>
       <c r="B13" t="n">
-        <v>98100</v>
+        <v>98106</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121226161</v>
+        <v>121225455</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,34 +2362,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473786</v>
+        <v>473813</v>
       </c>
       <c r="R14" t="n">
-        <v>7042884</v>
+        <v>7042912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2424,6 +2436,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2450,12 +2467,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2473,10 +2490,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298075</v>
+        <v>121298076</v>
       </c>
       <c r="B15" t="n">
-        <v>56558</v>
+        <v>90737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2489,53 +2506,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473885</v>
+        <v>473772</v>
       </c>
       <c r="R15" t="n">
-        <v>7042869</v>
+        <v>7042897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2578,12 +2586,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2601,10 +2630,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298076</v>
+        <v>121226161</v>
       </c>
       <c r="B16" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2617,44 +2646,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473772</v>
+        <v>473786</v>
       </c>
       <c r="R16" t="n">
-        <v>7042897</v>
+        <v>7042884</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2686,18 +2708,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2718,12 +2734,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,10 +2757,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121225455</v>
+        <v>121298031</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2779,7 +2795,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2789,17 +2805,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473813</v>
+        <v>473837</v>
       </c>
       <c r="R17" t="n">
-        <v>7042912</v>
+        <v>7042921</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2833,7 +2849,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2885,10 +2901,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298031</v>
+        <v>121298075</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>56559</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2901,16 +2917,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2918,12 +2934,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2937,13 +2957,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473837</v>
+        <v>473885</v>
       </c>
       <c r="R18" t="n">
-        <v>7042921</v>
+        <v>7042869</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2977,7 +2997,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2992,26 +3012,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121224936</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>121249306</v>
       </c>
       <c r="B3" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260654</v>
+        <v>121222886</v>
       </c>
       <c r="B4" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,44 +968,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473423</v>
+        <v>473389</v>
       </c>
       <c r="R4" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1048,7 +1049,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222886</v>
+        <v>121260654</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,45 +1108,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473389</v>
+        <v>473423</v>
       </c>
       <c r="R5" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1189,6 +1188,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
         <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292409</v>
+        <v>121292220</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>98107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,35 +1372,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1408,14 +1416,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473882</v>
+        <v>473457</v>
       </c>
       <c r="R7" t="n">
-        <v>7042892</v>
+        <v>7043473</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,6 +1469,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1469,24 +1478,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1504,10 +1498,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292659</v>
+        <v>121292409</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,37 +1514,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473835</v>
+        <v>473882</v>
       </c>
       <c r="R8" t="n">
-        <v>7042906</v>
+        <v>7042892</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,7 +1599,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1617,12 +1619,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1643,7 +1645,7 @@
         <v>121292347</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1784,10 +1786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292483</v>
+        <v>121225143</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1822,7 +1824,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1832,17 +1834,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473855</v>
+        <v>473844</v>
       </c>
       <c r="R10" t="n">
-        <v>7042902</v>
+        <v>7042901</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1928,10 +1930,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292522</v>
+        <v>121292659</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1967,14 +1969,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473855</v>
+        <v>473835</v>
       </c>
       <c r="R11" t="n">
-        <v>7042902</v>
+        <v>7042906</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2011,7 +2013,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2064,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121225143</v>
+        <v>121292483</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2102,7 +2104,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2112,17 +2114,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R12" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2208,10 +2210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292220</v>
+        <v>121292522</v>
       </c>
       <c r="B13" t="n">
-        <v>98106</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2220,58 +2222,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473457</v>
+        <v>473855</v>
       </c>
       <c r="R13" t="n">
-        <v>7043473</v>
+        <v>7042902</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2308,7 +2293,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2326,9 +2311,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121225455</v>
+        <v>121298031</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473813</v>
+        <v>473837</v>
       </c>
       <c r="R14" t="n">
-        <v>7042912</v>
+        <v>7042921</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2490,10 +2490,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298076</v>
+        <v>121226161</v>
       </c>
       <c r="B15" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2506,44 +2506,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473772</v>
+        <v>473786</v>
       </c>
       <c r="R15" t="n">
-        <v>7042897</v>
+        <v>7042884</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2575,18 +2568,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2607,12 +2594,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2630,10 +2617,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121226161</v>
+        <v>121225335</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2646,34 +2633,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473786</v>
+        <v>473813</v>
       </c>
       <c r="R16" t="n">
-        <v>7042884</v>
+        <v>7042912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2708,6 +2707,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2734,12 +2738,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2757,10 +2761,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298031</v>
+        <v>121298076</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2773,46 +2777,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473837</v>
+        <v>473772</v>
       </c>
       <c r="R17" t="n">
-        <v>7042921</v>
+        <v>7042897</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2849,7 +2848,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2858,6 +2857,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v>121298075</v>
       </c>
       <c r="B18" t="n">
-        <v>56559</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222886</v>
+        <v>121222957</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,39 +968,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473389</v>
+        <v>473391</v>
       </c>
       <c r="R4" t="n">
         <v>7043433</v>
@@ -1055,26 +1063,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121260654</v>
+        <v>121222886</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,44 +1096,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473423</v>
+        <v>473389</v>
       </c>
       <c r="R5" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1188,7 +1177,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1209,12 +1197,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,10 +1220,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1236,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R6" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,12 +1316,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292220</v>
+        <v>121292522</v>
       </c>
       <c r="B7" t="n">
-        <v>98107</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,58 +1372,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473457</v>
+        <v>473855</v>
       </c>
       <c r="R7" t="n">
-        <v>7043473</v>
+        <v>7042902</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1460,7 +1443,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,9 +1461,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1786,7 +1784,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121225143</v>
+        <v>121292483</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1824,7 +1822,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1834,17 +1832,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R10" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1930,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292659</v>
+        <v>121292220</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>98107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1942,41 +1940,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473835</v>
+        <v>473457</v>
       </c>
       <c r="R11" t="n">
-        <v>7042906</v>
+        <v>7043473</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2013,7 +2028,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,24 +2046,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292483</v>
+        <v>121225143</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -2104,7 +2104,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2114,17 +2114,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473855</v>
+        <v>473844</v>
       </c>
       <c r="R12" t="n">
-        <v>7042902</v>
+        <v>7042901</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292522</v>
+        <v>121292659</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -2249,14 +2249,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473855</v>
+        <v>473835</v>
       </c>
       <c r="R13" t="n">
-        <v>7042902</v>
+        <v>7042906</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2490,10 +2490,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121226161</v>
+        <v>121298076</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2506,37 +2506,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473786</v>
+        <v>473772</v>
       </c>
       <c r="R15" t="n">
-        <v>7042884</v>
+        <v>7042897</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2568,12 +2575,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2594,12 +2607,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2761,10 +2774,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298076</v>
+        <v>121226161</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2777,44 +2790,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473772</v>
+        <v>473786</v>
       </c>
       <c r="R17" t="n">
-        <v>7042897</v>
+        <v>7042884</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2846,18 +2852,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,53 +968,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R4" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1057,12 +1048,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1220,10 +1232,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,44 +1248,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R6" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1316,33 +1337,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292522</v>
+        <v>121292483</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,27 +1376,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -1443,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1461,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1473,12 +1481,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,7 +1504,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121292409</v>
+        <v>121225143</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1534,7 +1542,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1544,17 +1552,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473882</v>
+        <v>473844</v>
       </c>
       <c r="R8" t="n">
-        <v>7042892</v>
+        <v>7042901</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1784,10 +1792,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292483</v>
+        <v>121292220</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>98107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1796,35 +1804,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1832,14 +1848,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473855</v>
+        <v>473457</v>
       </c>
       <c r="R10" t="n">
-        <v>7042902</v>
+        <v>7043473</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1885,6 +1901,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1893,24 +1910,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1928,10 +1930,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292220</v>
+        <v>121292409</v>
       </c>
       <c r="B11" t="n">
-        <v>98107</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1940,43 +1942,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1984,14 +1978,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473457</v>
+        <v>473882</v>
       </c>
       <c r="R11" t="n">
-        <v>7043473</v>
+        <v>7042892</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2037,7 +2031,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2046,9 +2039,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2066,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121225143</v>
+        <v>121292522</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2082,49 +2090,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473844</v>
+        <v>473855</v>
       </c>
       <c r="R12" t="n">
-        <v>7042901</v>
+        <v>7042902</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2158,7 +2157,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2167,6 +2166,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121298031</v>
+        <v>121298075</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2379,12 +2379,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2398,13 +2402,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473837</v>
+        <v>473885</v>
       </c>
       <c r="R14" t="n">
-        <v>7042921</v>
+        <v>7042869</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2453,26 +2457,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2901,10 +2885,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298075</v>
+        <v>121298031</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,16 +2901,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2934,16 +2918,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2957,13 +2937,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473885</v>
+        <v>473837</v>
       </c>
       <c r="R18" t="n">
-        <v>7042869</v>
+        <v>7042921</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2997,7 +2977,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3012,6 +2992,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3026,6 +3026,145 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121616275</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473440</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7043357</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260654</v>
+        <v>121222957</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,44 +968,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473423</v>
+        <v>473391</v>
       </c>
       <c r="R4" t="n">
-        <v>7043436</v>
+        <v>7043433</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1048,33 +1057,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1232,10 +1220,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121222957</v>
+        <v>121260654</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,53 +1236,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungerbäcken, Lungerbäcken, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473391</v>
+        <v>473423</v>
       </c>
       <c r="R6" t="n">
-        <v>7043433</v>
+        <v>7043436</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,12 +1316,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Även stubbe från samma träd. # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292483</v>
+        <v>121292522</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,36 +1376,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -1452,7 +1443,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,6 +1452,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1481,12 +1473,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1648,10 +1640,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121292347</v>
+        <v>121292220</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>98107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1660,35 +1652,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Bodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473895</v>
+        <v>473457</v>
       </c>
       <c r="R9" t="n">
-        <v>7042857</v>
+        <v>7043473</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1749,6 +1749,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1757,24 +1758,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1792,10 +1778,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292220</v>
+        <v>121292409</v>
       </c>
       <c r="B10" t="n">
-        <v>98107</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1804,43 +1790,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1848,14 +1826,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodbäcken, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473457</v>
+        <v>473882</v>
       </c>
       <c r="R10" t="n">
-        <v>7043473</v>
+        <v>7042892</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1901,7 +1879,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1910,9 +1887,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Frisk-fuktig mark med gles grandominerad trädtäckning. Buskskikt med viden och fältskikt med kråkbär och lingon med inslag av örter och graminider.</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1930,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292409</v>
+        <v>121292659</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1946,46 +1938,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473882</v>
+        <v>473835</v>
       </c>
       <c r="R11" t="n">
-        <v>7042892</v>
+        <v>7042906</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2022,7 +2005,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,6 +2014,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2051,12 +2035,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,10 +2058,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121292522</v>
+        <v>121292483</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2090,27 +2074,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
@@ -2157,7 +2150,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,7 +2159,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2187,12 +2179,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2210,10 +2202,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292659</v>
+        <v>121292347</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2226,37 +2218,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473835</v>
+        <v>473895</v>
       </c>
       <c r="R13" t="n">
-        <v>7042906</v>
+        <v>7042857</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2302,7 +2303,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121298075</v>
+        <v>121225335</v>
       </c>
       <c r="B14" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2379,16 +2379,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2398,17 +2394,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473885</v>
+        <v>473813</v>
       </c>
       <c r="R14" t="n">
-        <v>7042869</v>
+        <v>7042912</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2457,6 +2453,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2614,7 +2630,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121225335</v>
+        <v>121298031</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2662,17 +2678,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473813</v>
+        <v>473837</v>
       </c>
       <c r="R16" t="n">
-        <v>7042912</v>
+        <v>7042921</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2706,7 +2722,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2758,10 +2774,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121226161</v>
+        <v>121298075</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2774,37 +2790,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473786</v>
+        <v>473885</v>
       </c>
       <c r="R17" t="n">
-        <v>7042884</v>
+        <v>7042869</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2836,6 +2868,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2848,26 +2885,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2885,10 +2902,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121298031</v>
+        <v>121226161</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2901,49 +2918,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473837</v>
+        <v>473786</v>
       </c>
       <c r="R18" t="n">
-        <v>7042921</v>
+        <v>7042884</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2975,11 +2980,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3166,6 +3166,1596 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121645674</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>473710</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7043106</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121638430</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>473824</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7042923</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121641599</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56560</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473958</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7042787</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121640405</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>473721</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7043000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om garnlav på flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121637994</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>473913</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7042910</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121640512</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473655</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7043131</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121639148</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>473788</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7043076</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121638928</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>473806</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7043006</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121645826</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>473804</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7042863</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121640169</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473734</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7043003</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121641017</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>473764</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7043028</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121645603</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vitmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>473775</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7043014</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -1360,10 +1360,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121292522</v>
+        <v>121292347</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,37 +1376,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473855</v>
+        <v>473895</v>
       </c>
       <c r="R7" t="n">
-        <v>7042902</v>
+        <v>7042857</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1443,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1461,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1473,12 +1481,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1499,7 +1507,7 @@
         <v>121225143</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1643,7 +1651,7 @@
         <v>121292220</v>
       </c>
       <c r="B9" t="n">
-        <v>98107</v>
+        <v>98112</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1778,10 +1786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121292409</v>
+        <v>121292659</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78614</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1794,46 +1802,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473882</v>
+        <v>473835</v>
       </c>
       <c r="R10" t="n">
-        <v>7042892</v>
+        <v>7042906</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1870,7 +1869,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1879,6 +1878,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121292659</v>
+        <v>121292409</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1938,37 +1938,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473835</v>
+        <v>473882</v>
       </c>
       <c r="R11" t="n">
-        <v>7042906</v>
+        <v>7042892</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2005,7 +2014,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2014,7 +2023,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2035,12 +2043,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2061,7 +2069,7 @@
         <v>121292483</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2202,10 +2210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121292347</v>
+        <v>121292522</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>78614</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2218,46 +2226,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473895</v>
+        <v>473855</v>
       </c>
       <c r="R13" t="n">
-        <v>7042857</v>
+        <v>7042902</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2294,7 +2293,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,6 +2302,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121225335</v>
+        <v>121298076</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2362,49 +2362,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473813</v>
+        <v>473772</v>
       </c>
       <c r="R14" t="n">
-        <v>7042912</v>
+        <v>7042897</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2447,6 +2442,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2467,12 +2463,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2490,10 +2486,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121298076</v>
+        <v>121298031</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2506,41 +2502,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473772</v>
+        <v>473837</v>
       </c>
       <c r="R15" t="n">
-        <v>7042897</v>
+        <v>7042921</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2577,7 +2578,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2586,7 +2587,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121298031</v>
+        <v>121225455</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2678,17 +2678,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473837</v>
+        <v>473813</v>
       </c>
       <c r="R16" t="n">
-        <v>7042921</v>
+        <v>7042912</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran som troligen kan ha skapats under 2024. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121298075</v>
+        <v>121226161</v>
       </c>
       <c r="B17" t="n">
-        <v>56560</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2790,53 +2790,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473885</v>
+        <v>473786</v>
       </c>
       <c r="R17" t="n">
-        <v>7042869</v>
+        <v>7042884</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2868,11 +2852,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2885,6 +2864,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2902,10 +2901,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121226161</v>
+        <v>121298075</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>56561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2918,37 +2917,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473786</v>
+        <v>473885</v>
       </c>
       <c r="R18" t="n">
-        <v>7042884</v>
+        <v>7042869</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2980,6 +2995,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 49972-2024.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2992,26 +3012,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
         <v>121616275</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121645674</v>
+        <v>121640169</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3184,49 +3184,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473710</v>
+        <v>473734</v>
       </c>
       <c r="R20" t="n">
-        <v>7043106</v>
+        <v>7043003</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3250,17 +3238,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på en gran.</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3289,12 +3272,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3312,10 +3295,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121638430</v>
+        <v>121640405</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3352,13 +3335,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473824</v>
+        <v>473721</v>
       </c>
       <c r="R21" t="n">
-        <v>7042923</v>
+        <v>7043000</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3392,7 +3375,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flertalet granar.</t>
+          <t>Gott om garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3444,10 +3427,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121641599</v>
+        <v>121641017</v>
       </c>
       <c r="B22" t="n">
-        <v>56560</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3460,48 +3443,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473958</v>
+        <v>473764</v>
       </c>
       <c r="R22" t="n">
-        <v>7042787</v>
+        <v>7043028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3536,6 +3505,11 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3548,6 +3522,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3565,10 +3559,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121640405</v>
+        <v>121640512</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3605,10 +3599,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473721</v>
+        <v>473655</v>
       </c>
       <c r="R23" t="n">
-        <v>7043000</v>
+        <v>7043131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3641,11 +3635,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3697,10 +3686,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121637994</v>
+        <v>121645826</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3713,37 +3702,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473913</v>
+        <v>473804</v>
       </c>
       <c r="R24" t="n">
-        <v>7042910</v>
+        <v>7042863</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3767,17 +3768,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3806,12 +3807,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3829,10 +3830,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121640512</v>
+        <v>121637994</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3869,10 +3870,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473655</v>
+        <v>473913</v>
       </c>
       <c r="R25" t="n">
-        <v>7043131</v>
+        <v>7042910</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3905,6 +3906,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3956,10 +3962,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121639148</v>
+        <v>121645603</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3972,34 +3978,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473788</v>
+        <v>473775</v>
       </c>
       <c r="R26" t="n">
-        <v>7043076</v>
+        <v>7043014</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4026,17 +4039,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4045,6 +4053,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4065,12 +4074,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4088,10 +4097,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121638928</v>
+        <v>121638430</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4128,13 +4137,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473806</v>
+        <v>473824</v>
       </c>
       <c r="R27" t="n">
-        <v>7043006</v>
+        <v>7042923</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4168,7 +4177,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Rikligt med garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4220,10 +4229,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121645826</v>
+        <v>121645674</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4258,7 +4267,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4268,14 +4277,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473804</v>
+        <v>473710</v>
       </c>
       <c r="R28" t="n">
-        <v>7042863</v>
+        <v>7043106</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4312,7 +4321,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Gott om färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4341,12 +4350,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4364,10 +4373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121640169</v>
+        <v>121639148</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4404,10 +4413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473734</v>
+        <v>473788</v>
       </c>
       <c r="R29" t="n">
-        <v>7043003</v>
+        <v>7043076</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4440,6 +4449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4491,10 +4505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121641017</v>
+        <v>121641599</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>56561</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4507,34 +4521,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473764</v>
+        <v>473958</v>
       </c>
       <c r="R30" t="n">
-        <v>7043028</v>
+        <v>7042787</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4569,11 +4597,6 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4586,26 +4609,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4623,10 +4626,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121645603</v>
+        <v>121638928</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4639,41 +4642,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473775</v>
+        <v>473806</v>
       </c>
       <c r="R31" t="n">
-        <v>7043014</v>
+        <v>7043006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4700,12 +4696,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4714,7 +4715,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -3168,7 +3168,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121640512</v>
+        <v>121638430</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473655</v>
+        <v>473824</v>
       </c>
       <c r="R20" t="n">
-        <v>7043131</v>
+        <v>7042923</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3244,6 +3244,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,7 +3300,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121640405</v>
+        <v>121640512</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473721</v>
+        <v>473655</v>
       </c>
       <c r="R21" t="n">
-        <v>7043000</v>
+        <v>7043131</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3371,11 +3376,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121641017</v>
+        <v>121645603</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3443,34 +3443,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473764</v>
+        <v>473775</v>
       </c>
       <c r="R22" t="n">
-        <v>7043028</v>
+        <v>7043014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3497,17 +3504,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3516,6 +3518,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3536,12 +3539,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3559,10 +3562,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121645603</v>
+        <v>121641599</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>56561</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3575,41 +3578,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473775</v>
+        <v>473958</v>
       </c>
       <c r="R23" t="n">
-        <v>7043014</v>
+        <v>7042787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3636,12 +3646,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3650,33 +3660,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3694,10 +3683,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121641599</v>
+        <v>121640405</v>
       </c>
       <c r="B24" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3710,48 +3699,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473958</v>
+        <v>473721</v>
       </c>
       <c r="R24" t="n">
-        <v>7042787</v>
+        <v>7043000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3786,6 +3761,11 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om garnlav på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3798,6 +3778,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121640169</v>
+        <v>121638928</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473734</v>
+        <v>473806</v>
       </c>
       <c r="R25" t="n">
-        <v>7043003</v>
+        <v>7043006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3891,6 +3891,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3942,7 +3947,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121645674</v>
+        <v>121645826</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3980,7 +3985,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473710</v>
+        <v>473804</v>
       </c>
       <c r="R26" t="n">
-        <v>7043106</v>
+        <v>7042863</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4034,7 +4039,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4063,12 +4068,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4086,10 +4091,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121638430</v>
+        <v>121645674</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4102,37 +4107,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473824</v>
+        <v>473710</v>
       </c>
       <c r="R27" t="n">
-        <v>7042923</v>
+        <v>7043106</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4156,17 +4173,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flertalet granar.</t>
+          <t>Gott om färska ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4195,12 +4212,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4218,7 +4235,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121637994</v>
+        <v>121640169</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -4258,10 +4275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473913</v>
+        <v>473734</v>
       </c>
       <c r="R28" t="n">
-        <v>7042910</v>
+        <v>7043003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4294,11 +4311,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4350,7 +4362,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121638928</v>
+        <v>121637994</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -4390,10 +4402,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473806</v>
+        <v>473913</v>
       </c>
       <c r="R29" t="n">
-        <v>7043006</v>
+        <v>7042910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4430,7 +4442,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Långväxt garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4482,10 +4494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121645826</v>
+        <v>121639148</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4498,49 +4510,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473804</v>
+        <v>473788</v>
       </c>
       <c r="R30" t="n">
-        <v>7042863</v>
+        <v>7043076</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4564,17 +4564,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121639148</v>
+        <v>121641017</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473788</v>
+        <v>473764</v>
       </c>
       <c r="R31" t="n">
-        <v>7043076</v>
+        <v>7043028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 49972-2024 artfynd.xlsx
+++ b/artfynd/A 49972-2024 artfynd.xlsx
@@ -3300,7 +3300,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121640512</v>
+        <v>121640169</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473655</v>
+        <v>473734</v>
       </c>
       <c r="R21" t="n">
-        <v>7043131</v>
+        <v>7043003</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121645603</v>
+        <v>121645674</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3443,44 +3443,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473775</v>
+        <v>473710</v>
       </c>
       <c r="R22" t="n">
-        <v>7043014</v>
+        <v>7043106</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3512,13 +3517,17 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3539,12 +3548,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3562,10 +3571,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121641599</v>
+        <v>121638928</v>
       </c>
       <c r="B23" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3578,48 +3587,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473958</v>
+        <v>473806</v>
       </c>
       <c r="R23" t="n">
-        <v>7042787</v>
+        <v>7043006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3654,6 +3649,11 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på flera granar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3666,6 +3666,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3683,10 +3703,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121640405</v>
+        <v>121645826</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3699,37 +3719,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473721</v>
+        <v>473804</v>
       </c>
       <c r="R24" t="n">
-        <v>7043000</v>
+        <v>7042863</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3753,17 +3785,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flertalet granar.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3792,12 +3824,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3815,7 +3847,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121638928</v>
+        <v>121639148</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3855,10 +3887,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473806</v>
+        <v>473788</v>
       </c>
       <c r="R25" t="n">
-        <v>7043006</v>
+        <v>7043076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3895,7 +3927,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på flera granar.</t>
+          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3947,10 +3979,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121645826</v>
+        <v>121641599</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3963,16 +3995,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3980,12 +4012,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3995,17 +4029,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Österlångan, Aspås, Jmt</t>
+          <t>Vitmossaflon, Lundsjön, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473804</v>
+        <v>473958</v>
       </c>
       <c r="R26" t="n">
-        <v>7042863</v>
+        <v>7042787</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4029,17 +4063,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4054,26 +4083,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4091,10 +4100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121645674</v>
+        <v>121637994</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4107,49 +4116,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473710</v>
+        <v>473913</v>
       </c>
       <c r="R27" t="n">
-        <v>7043106</v>
+        <v>7042910</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4173,17 +4170,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en gran.</t>
+          <t>Långväxt garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4212,12 +4209,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4235,7 +4232,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121640169</v>
+        <v>121641017</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -4275,10 +4272,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473734</v>
+        <v>473764</v>
       </c>
       <c r="R28" t="n">
-        <v>7043003</v>
+        <v>7043028</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4311,6 +4308,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4362,7 +4364,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121637994</v>
+        <v>121640405</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -4402,10 +4404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473913</v>
+        <v>473721</v>
       </c>
       <c r="R29" t="n">
-        <v>7042910</v>
+        <v>7043000</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4442,7 +4444,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flertalet granar.</t>
+          <t>Gott om garnlav på flertalet granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4494,7 +4496,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121639148</v>
+        <v>121640512</v>
       </c>
       <c r="B30" t="n">
         <v>78616</v>
@@ -4534,10 +4536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473788</v>
+        <v>473655</v>
       </c>
       <c r="R30" t="n">
-        <v>7043076</v>
+        <v>7043131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4570,11 +4572,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på flera granar blandat med andra hänglavar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4626,10 +4623,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121641017</v>
+        <v>121645603</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4642,34 +4639,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vitmossaflon, Vitmossaflon, Jmt</t>
+          <t>Vitmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473764</v>
+        <v>473775</v>
       </c>
       <c r="R31" t="n">
-        <v>7043028</v>
+        <v>7043014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4696,17 +4700,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4715,6 +4714,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
